--- a/specs/perelinkovka-drugie-uslugi.xlsx
+++ b/specs/perelinkovka-drugie-uslugi.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Куда встаёт блок" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Проверка по критериям" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Новая карта" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Воронка" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проверка по критериям'!$A$6:$J$122</definedName>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -99,17 +100,26 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="008E9142"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="001B1B1B"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00C32F55"/>
+      <color rgb="006C6D60"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="008E9142"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -134,6 +144,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FDF4E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF0DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -163,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -237,13 +257,23 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -253,7 +283,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -2998,12 +3028,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H64" s="12" t="inlineStr">
-        <is>
-          <t>оставить</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="inlineStr"/>
+      <c r="H64" s="13" t="inlineStr">
+        <is>
+          <t>заменить</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (1 · абонентское бухобслуживание)</t>
+        </is>
+      </c>
       <c r="J64" s="11" t="inlineStr"/>
     </row>
     <row r="65" ht="30" customHeight="1">
@@ -3550,12 +3584,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H79" s="12" t="inlineStr">
-        <is>
-          <t>оставить</t>
-        </is>
-      </c>
-      <c r="I79" s="11" t="inlineStr"/>
+      <c r="H79" s="13" t="inlineStr">
+        <is>
+          <t>заменить</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (1 · абонентское бухобслуживание)</t>
+        </is>
+      </c>
       <c r="J79" s="11" t="inlineStr"/>
     </row>
     <row r="80" ht="30" customHeight="1">
@@ -7712,20 +7750,24 @@
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>Составление договоров</t>
+          <t>Бухгалтерское сопровождение</t>
         </is>
       </c>
       <c r="G64" s="22" t="inlineStr">
         <is>
-          <t>/yuristy-dlya-biznesa/sostavlenie-dogovorov/</t>
-        </is>
-      </c>
-      <c r="H64" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I64" s="9" t="inlineStr"/>
+          <t>/bukhgalterskie-uslugi/abonentskoe-obsluzhivanie/</t>
+        </is>
+      </c>
+      <c r="H64" s="14" t="inlineStr">
+        <is>
+          <t>① абонентское бухобслуживание</t>
+        </is>
+      </c>
+      <c r="I64" s="23" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="J64" s="12" t="inlineStr"/>
       <c r="K64" s="11" t="inlineStr"/>
     </row>
@@ -8331,20 +8373,24 @@
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>Составление договоров</t>
+          <t>Бухгалтерское сопровождение</t>
         </is>
       </c>
       <c r="G79" s="22" t="inlineStr">
         <is>
-          <t>/yuristy-dlya-biznesa/sostavlenie-dogovorov/</t>
-        </is>
-      </c>
-      <c r="H79" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="9" t="inlineStr"/>
+          <t>/bukhgalterskie-uslugi/abonentskoe-obsluzhivanie/</t>
+        </is>
+      </c>
+      <c r="H79" s="14" t="inlineStr">
+        <is>
+          <t>① абонентское бухобслуживание</t>
+        </is>
+      </c>
+      <c r="I79" s="23" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="J79" s="12" t="inlineStr"/>
       <c r="K79" s="11" t="inlineStr"/>
     </row>
@@ -8536,17 +8582,17 @@
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>Представительство в судах</t>
+          <t>Бухгалтерское сопровождение</t>
         </is>
       </c>
       <c r="G84" s="24" t="inlineStr">
         <is>
-          <t>/yuristy-dlya-biznesa/predstavitelstvo-v-sudakh/</t>
-        </is>
-      </c>
-      <c r="H84" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>/bukhgalterskie-uslugi/abonentskoe-obsluzhivanie/</t>
+        </is>
+      </c>
+      <c r="H84" s="19" t="inlineStr">
+        <is>
+          <t>① абонентское бухобслуживание</t>
         </is>
       </c>
       <c r="I84" s="15" t="inlineStr"/>
@@ -8618,17 +8664,17 @@
       </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>Бухгалтерское сопровождение</t>
+          <t>Представительство в судах</t>
         </is>
       </c>
       <c r="G86" s="24" t="inlineStr">
         <is>
-          <t>/bukhgalterskie-uslugi/abonentskoe-obsluzhivanie/</t>
-        </is>
-      </c>
-      <c r="H86" s="19" t="inlineStr">
-        <is>
-          <t>① абонентское бухобслуживание</t>
+          <t>/yuristy-dlya-biznesa/predstavitelstvo-v-sudakh/</t>
+        </is>
+      </c>
+      <c r="H86" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr"/>
@@ -10374,7 +10420,1403 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:D73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="86" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Что приводит клиента в главные услуги</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Логика блока «Другие услуги»: человек пришёл на страницу не просто так. Его ситуация говорит о проблеме,</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>а следующая услуга эту проблему закрывает. Пример: восстановление учёта — это улика, что прежний бухгалтер</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>не справился, значит клиенту нужен не только ремонт прошлого, но и новый бухгалтер на будущее.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>Чем сильнее вход, тем выше ссылка стоит в блоке. У всех сильных входов она первой карточкой.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>Входы в абонентское бухгалтерское обслуживание — приоритет 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Страница клиента</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Сила входа</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Что говорит ситуация клиента</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Ссылка в блоке</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Восстановление учёта</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>сильный</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Учёт разваливали месяцами, а то и годами. Это прямая улика: прежний бухгалтер не справился. Клиенту нужен не только ремонт прошлого, но и новый бухгалтер на будущее</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Защита от налоговой</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>сильный</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Проверка пришла и нашла нарушения. Это доказательство, что учёт вели плохо, полученное от самой налоговой</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Инициативный аудит бухгалтерии</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>сильный</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Аудит заказывают, когда своей бухгалтерии уже не доверяют. Аудит находит ошибки и подтверждает подозрение — бухгалтера пора менять</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Консультация бухгалтера</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>сильный</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Задаёт вопросы чужим бухгалтерам. Значит, своему или не доверяет, или его нет</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Подбор главбухов</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>сильный</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Клиент уже признал, что бухгалтерия не закрыта, и ищет человека в штат. Мы предлагаем не нанимать одного, а получить команду дешевле</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Регистрация и ликвидация бизнеса</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>сильный</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Компании ноль дней, бухгалтера нет вообще. Решение принимается прямо сейчас, и второй раз этот момент не повторится</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Внесение изменений в ЕГРЮЛ и ЕГРИП</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Меняют директора или участника. Это типичный момент, когда меняют и бухгалтера</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Воинский учёт</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Новая обязанность со штрафами, которую ведут кадры и бухгалтерия. Если их нет, нужны обе функции</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Заполнение деклараций</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Сдаёт отчётность разово. Значит, постоянного бухгалтера нет либо ему не доверяют отчётность</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Платит больше, чем мог бы. Значит, бухгалтер только считает, а планированием не занимается</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Правовой аудит</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Проверяют риски в документах. Учётные риски вскрываются там же</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Сопровождение ВЭД</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Учёт ВЭД сложный: НДС 0%, валютный контроль, подтверждение ставки. Рядовой бухгалтер его не тянет</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Споры в трудовых отношениях</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Трудовой спор почти всегда растёт из неправильно оформленных документов и ошибок в расчётах — это зона бухгалтерии</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Управленческий финансовый учёт</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Собственник не видит цифр своего бизнеса. Бухгалтерия делает отчётность для налоговой, а не для него</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Уже доверил нам одну функцию. Вторую отдать психологически проще, чем первую</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Взыскание долгов</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>слабый</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Долги контрагентов — не признак плохого учёта</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Защита интеллектуальных прав</t>
+        </is>
+      </c>
+      <c r="B25" s="28" t="inlineStr">
+        <is>
+          <t>слабый</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Интеллектуальные права с бухгалтерией не связаны</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Представительство в судах</t>
+        </is>
+      </c>
+      <c r="B26" s="28" t="inlineStr">
+        <is>
+          <t>слабый</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Судебный процесс мало говорит о состоянии бухгалтерии</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Регистрация товарного знака</t>
+        </is>
+      </c>
+      <c r="B27" s="28" t="inlineStr">
+        <is>
+          <t>слабый</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Товарный знак с бухгалтерией не связан</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Составление договоров</t>
+        </is>
+      </c>
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t>слабый</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Разовая юридическая работа, о бухгалтерии ничего не говорит</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Судебная бухгалтерская экспертиза</t>
+        </is>
+      </c>
+      <c r="B29" s="28" t="inlineStr">
+        <is>
+          <t>слабый</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Экспертиза чаще про спор с контрагентом, чем про собственный учёт</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Вернуть налоги в офисе</t>
+        </is>
+      </c>
+      <c r="B30" s="28" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>B2C: физлицо с налоговым вычетом не клиент бухобслуживания компаний</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>Вернуть налоги онлайн</t>
+        </is>
+      </c>
+      <c r="B31" s="28" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>B2C: физлицо с налоговым вычетом не клиент бухобслуживания компаний</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Декларация 3-НДФЛ</t>
+        </is>
+      </c>
+      <c r="B32" s="28" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>B2C: физлицо с налоговым вычетом не клиент бухобслуживания компаний</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для крупного бизнеса</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Это категория самого абонентского обслуживания, а не отдельная услуга</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для малого бизнеса</t>
+        </is>
+      </c>
+      <c r="B34" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Это категория самого абонентского обслуживания, а не отдельная услуга</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для среднего бизнеса</t>
+        </is>
+      </c>
+      <c r="B35" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Это категория самого абонентского обслуживания, а не отдельная услуга</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>Входы в финансовый и налоговый консалтинг — приоритет 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Страница клиента</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Сила входа</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Что говорит ситуация клиента</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Ссылка в блоке</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для крупного бизнеса</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>сильный</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>На таком обороте управленческий учёт и налоговое планирование обязательны</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>Управленческий финансовый учёт  (поз. 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для среднего бизнеса</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>сильный</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Бизнес дорос до размера, когда собственник перестаёт видеть цифры сам</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>Управленческий финансовый учёт  (поз. 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>сильный</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Клиент на обслуживании вырос. Учёт в порядке, а управленческих цифр и налогового планирования нет — это следующая покупка, и продавать её проще всего</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>Управленческий финансовый учёт, Оптимизация налогообложения  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>Восстановление учёта</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>сильный</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>Учёт восстановили. Логичный следующий шаг — проверить, что теперь всё корректно</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Инициативный аудит бухгалтерии, Оптимизация налогообложения  (поз. 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>Защита от налоговой</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>сильный</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>После проверки клиент хочет снижать нагрузку законно, а не рисковать снова</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>Инициативный аудит бухгалтерии, Оптимизация налогообложения  (поз. 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для малого бизнеса</t>
+        </is>
+      </c>
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>УСН: выбор режима, контроль порогов, риск дробления — это уже налоговый консалтинг</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения  (поз. 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>Взыскание долгов</t>
+        </is>
+      </c>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>Во взыскании долга нужна экспертиза расчётов</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>Судебная бухгалтерская экспертиза  (поз. 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>Заполнение деклараций</t>
+        </is>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>Сдаёт декларации — значит, платит налоги, значит, есть что оптимизировать</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения, Инициативный аудит бухгалтерии  (поз. 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>Консультация бухгалтера</t>
+        </is>
+      </c>
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>Разовый вопрос обычно оказывается верхушкой системной задачи</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>Инициативный аудит бухгалтерии  (поз. 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>Подбор главбухов</t>
+        </is>
+      </c>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>Ищут главбуха часто потому, что не хватает управленческой отчётности</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>Управленческий финансовый учёт  (поз. 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>Правовой аудит</t>
+        </is>
+      </c>
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>Правовой аудит естественно продолжается аудитом бухгалтерии</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>Инициативный аудит бухгалтерии  (поз. 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>Представительство в судах</t>
+        </is>
+      </c>
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>В судебном споре о деньгах нужна судебная бухгалтерская экспертиза</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>Судебная бухгалтерская экспертиза  (поз. 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>Сопровождение ВЭД</t>
+        </is>
+      </c>
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>ВЭД — это НДС 0%, валютный контроль и налоговые риски</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения  (поз. 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>Составление договоров</t>
+        </is>
+      </c>
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>Налоговые последствия сделки закладываются в договоре, а не после него</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения  (поз. 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="26" t="inlineStr">
+        <is>
+          <t>Входы в юридическое обслуживание бизнеса — приоритет 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Страница клиента</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Сила входа</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Что говорит ситуация клиента</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Ссылка в блоке</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>Взыскание долгов</t>
+        </is>
+      </c>
+      <c r="B58" s="27" t="inlineStr">
+        <is>
+          <t>сильный</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>Долги повторяются. Разовое взыскание не решает причину</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание  (поз. 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>Правовой аудит</t>
+        </is>
+      </c>
+      <c r="B59" s="27" t="inlineStr">
+        <is>
+          <t>сильный</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>Аудит нашёл риски. Закрывать их надо постоянно, а не разово</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>Представительство в судах</t>
+        </is>
+      </c>
+      <c r="B60" s="27" t="inlineStr">
+        <is>
+          <t>сильный</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>Судебный процесс убеждает лучше любой рекламы: юрист нужен постоянно</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание  (поз. 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>Регистрация и ликвидация бизнеса</t>
+        </is>
+      </c>
+      <c r="B61" s="27" t="inlineStr">
+        <is>
+          <t>сильный</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>Компанию зарегистрировали — дальше нужны договоры, кадры, сопровождение</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание  (поз. 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>Составление договоров</t>
+        </is>
+      </c>
+      <c r="B62" s="27" t="inlineStr">
+        <is>
+          <t>сильный</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>Договоры нужны постоянно, а не один раз. Разовая работа показывает это клиенту</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>Споры в трудовых отношениях</t>
+        </is>
+      </c>
+      <c r="B63" s="27" t="inlineStr">
+        <is>
+          <t>сильный</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>Трудовые споры повторяются, пока не выстроены кадровые документы</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>Юридическая консультация</t>
+        </is>
+      </c>
+      <c r="B64" s="27" t="inlineStr">
+        <is>
+          <t>сильный</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>Разовая консультация — прямой и самый дешёвый вход в абонентскую юрподдержку</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание  (поз. 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для крупного бизнеса</t>
+        </is>
+      </c>
+      <c r="B65" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>На таком обороте юридические вопросы возникают постоянно</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание  (поз. 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерия для среднего бизнеса</t>
+        </is>
+      </c>
+      <c r="B66" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>На таком обороте юридические вопросы возникают постоянно</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание  (поз. 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>Бухгалтерское сопровождение</t>
+        </is>
+      </c>
+      <c r="B67" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>Комплексное обслуживание: бухгалтерия и юристы в одном месте</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание  (поз. 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>Внесение изменений в ЕГРЮЛ и ЕГРИП</t>
+        </is>
+      </c>
+      <c r="B68" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>Регистрационные действия повторяются по мере роста компании</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание  (поз. 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>Воинский учёт</t>
+        </is>
+      </c>
+      <c r="B69" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>Воинский учёт — зона с проверками и штрафами, нужна юридическая подстраховка</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание  (поз. 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>Защита интеллектуальных прав</t>
+        </is>
+      </c>
+      <c r="B70" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>Защита прав — часть постоянной юридической работы, а не разовая акция</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание  (поз. 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>Регистрация товарного знака</t>
+        </is>
+      </c>
+      <c r="B71" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>Знак зарегистрировали — дальше его надо защищать</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание  (поз. 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>Сопровождение ВЭД</t>
+        </is>
+      </c>
+      <c r="B72" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>ВЭД требует постоянного юридического сопровождения</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание  (поз. 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>Судебная бухгалтерская экспертиза</t>
+        </is>
+      </c>
+      <c r="B73" s="23" t="inlineStr">
+        <is>
+          <t>средний</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>Экспертиза нужна в споре, а спор ведёт юрист</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>Юридическое обслуживание  (поз. 2)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -10428,11 +11870,11 @@
         <v>14</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="D4" s="25" t="inlineStr">
-        <is>
-          <t>+4</t>
+        <v>20</v>
+      </c>
+      <c r="D4" s="29" t="inlineStr">
+        <is>
+          <t>+6</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -10453,14 +11895,14 @@
       <c r="C5" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>+13</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>вернули ссылки с бухгалтерских страниц — см. вопрос ниже</t>
+          <t>вернули ссылки с бухгалтерских страниц — решение ниже</t>
         </is>
       </c>
     </row>
@@ -10476,7 +11918,7 @@
       <c r="C6" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
@@ -10497,11 +11939,11 @@
         <v>74</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>52</v>
-      </c>
-      <c r="D7" s="26" t="inlineStr">
-        <is>
-          <t>-22</t>
+        <v>50</v>
+      </c>
+      <c r="D7" s="30" t="inlineStr">
+        <is>
+          <t>-24</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -10511,7 +11953,7 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Входящие ссылки на приоритетные страницы</t>
         </is>
@@ -10545,192 +11987,216 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>Бухгалтерское сопровождение</t>
         </is>
       </c>
-      <c r="B11" s="29" t="n">
+      <c r="B11" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="C11" s="29" t="n">
-        <v>18</v>
-      </c>
-      <c r="D11" s="30" t="inlineStr">
+      <c r="C11" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t>+6</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>① абонентское бухобслуживание</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>Оптимизация налогообложения</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>+6</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>② фин. и налоговый консалтинг</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>Инициативный аудит бухгалтерии</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>② фин. и налоговый консалтинг</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>Управленческий финансовый учёт</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="34" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="E11" s="28" t="inlineStr">
-        <is>
-          <t>① абонентское бухобслуживание</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
-        <is>
-          <t>Оптимизация налогообложения</t>
-        </is>
-      </c>
-      <c r="B12" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="C12" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="D12" s="30" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E14" s="32" t="inlineStr">
         <is>
           <t>② фин. и налоговый консалтинг</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>Инициативный аудит бухгалтерии</t>
-        </is>
-      </c>
-      <c r="B13" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" s="30" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="inlineStr">
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>Судебная бухгалтерская экспертиза</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="34" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
         <is>
           <t>② фин. и налоговый консалтинг</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="28" t="inlineStr">
-        <is>
-          <t>Управленческий финансовый учёт</t>
-        </is>
-      </c>
-      <c r="B14" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" s="30" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
-      <c r="E14" s="28" t="inlineStr">
-        <is>
-          <t>② фин. и налоговый консалтинг</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>Судебная бухгалтерская экспертиза</t>
-        </is>
-      </c>
-      <c r="B15" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="30" t="inlineStr">
-        <is>
-          <t>+0</t>
-        </is>
-      </c>
-      <c r="E15" s="28" t="inlineStr">
-        <is>
-          <t>② фин. и налоговый консалтинг</t>
-        </is>
-      </c>
-    </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="28" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>Юридическое обслуживание</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="D16" s="30" t="inlineStr">
+      <c r="D16" s="34" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="E16" s="28" t="inlineStr">
+      <c r="E16" s="32" t="inlineStr">
         <is>
           <t>③ юридическое обслуживание</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="31" t="inlineStr">
-        <is>
-          <t>ВОПРОС, КОТОРЫЙ НУЖНО РЕШИТЬ</t>
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>ФИНАНСОВЫЙ КОНСАЛТИНГ И БУХГАЛТЕРСКИЕ УСЛУГИ</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="32" t="inlineStr">
-        <is>
-          <t>В прошлой версии мы убрали финансовый консалтинг со страниц бухгалтерских услуг — по вашей правке.</t>
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t>Решение принято: блок «Другие услуги» — это допродажа, а не пункт меню, поэтому ссылки</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>Но консалтинг стоит вторым в приоритете продаж, а бухгалтерский раздел — самый посещаемый.</t>
+      <c r="A20" s="36" t="inlineStr">
+        <is>
+          <t>с бухгалтерских страниц на финансовый консалтинг в нём остаются. Их 11.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="32" t="inlineStr">
-        <is>
-          <t>Чтобы приоритет работал, в новой карте эти 11 ссылок вернулись.</t>
-        </is>
-      </c>
+      <c r="A21" s="36" t="inlineStr"/>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="32" t="inlineStr">
-        <is>
-          <t>Если решение убрать консалтинг из бухгалтерии было принципиальным — скажите, откачу.</t>
+      <c r="A22" s="36" t="inlineStr">
+        <is>
+          <t>Отдельно и не отменяется: из мега-меню в ветке «Бухгалтерские услуги» пункты</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="32" t="inlineStr">
-        <is>
-          <t>Тогда приоритет 2 останется с 15 ссылками вместо 26, и почти все — изнутри самого раздела консалтинга.</t>
+      <c r="A23" s="36" t="inlineStr">
+        <is>
+          <t>«Инициативный аудит» и «Финансовый / Налоговый консалтинг» убираются — это задача 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="36" t="inlineStr">
+        <is>
+          <t>Там они создают ложную иерархию и дублируют анкоры на один и тот же адрес.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="36" t="inlineStr"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="36" t="inlineStr">
+        <is>
+          <t>Раздел «Декларации 3-НДФЛ» намеренно оставлен без приоритетных ссылок: это B2C-воронка,</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="36" t="inlineStr">
+        <is>
+          <t>физлицо с вычетом не клиент бухобслуживания компаний.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="9">
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A27:E27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/specs/perelinkovka-drugie-uslugi.xlsx
+++ b/specs/perelinkovka-drugie-uslugi.xlsx
@@ -3882,7 +3882,11 @@
           <t>Зарегистрируем бренд</t>
         </is>
       </c>
-      <c r="H86" s="10" t="inlineStr"/>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>зелёная</t>
+        </is>
+      </c>
       <c r="I86" s="8" t="inlineStr"/>
     </row>
     <row r="87" ht="26" customHeight="1">
@@ -4412,7 +4416,11 @@
           <t>Когда вопрос сложнее вычета</t>
         </is>
       </c>
-      <c r="H100" s="6" t="inlineStr"/>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>зелёная</t>
+        </is>
+      </c>
       <c r="I100" s="4" t="inlineStr"/>
     </row>
     <row r="101" ht="26" customHeight="1">
@@ -4449,7 +4457,11 @@
           <t>Подготовим и сдадим отчётность</t>
         </is>
       </c>
-      <c r="H101" s="6" t="inlineStr"/>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>зелёная</t>
+        </is>
+      </c>
       <c r="I101" s="4" t="inlineStr"/>
     </row>
     <row r="102" ht="26" customHeight="1">
@@ -4560,7 +4572,11 @@
           <t>Когда вопрос сложнее вычета</t>
         </is>
       </c>
-      <c r="H104" s="10" t="inlineStr"/>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t>зелёная</t>
+        </is>
+      </c>
       <c r="I104" s="8" t="inlineStr"/>
     </row>
     <row r="105" ht="26" customHeight="1">
@@ -4597,7 +4613,11 @@
           <t>Подготовим и сдадим отчётность</t>
         </is>
       </c>
-      <c r="H105" s="10" t="inlineStr"/>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>зелёная</t>
+        </is>
+      </c>
       <c r="I105" s="8" t="inlineStr"/>
     </row>
     <row r="106" ht="26" customHeight="1">
@@ -4708,7 +4728,11 @@
           <t>Подготовим и сдадим отчётность</t>
         </is>
       </c>
-      <c r="H108" s="6" t="inlineStr"/>
+      <c r="H108" s="7" t="inlineStr">
+        <is>
+          <t>зелёная</t>
+        </is>
+      </c>
       <c r="I108" s="4" t="inlineStr"/>
     </row>
     <row r="109" ht="26" customHeight="1">
@@ -4745,7 +4769,11 @@
           <t>Когда вопрос сложнее вычета</t>
         </is>
       </c>
-      <c r="H109" s="6" t="inlineStr"/>
+      <c r="H109" s="7" t="inlineStr">
+        <is>
+          <t>зелёная</t>
+        </is>
+      </c>
       <c r="I109" s="4" t="inlineStr"/>
     </row>
     <row r="110" ht="26" customHeight="1">

--- a/specs/perelinkovka-drugie-uslugi.xlsx
+++ b/specs/perelinkovka-drugie-uslugi.xlsx
@@ -667,7 +667,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Увидеть цифры, а не только отчётность</t>
+          <t>Если непонятно, где прибыль</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Если за прошлые годы беспорядок</t>
+          <t>Приведём в порядок прошлые периоды</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Чтобы учёт больше не разваливался</t>
+          <t>Возьмём учёт и отчётность на себя</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Проверим, всё ли теперь в порядке</t>
+          <t>Проверим учёт раньше, чем налоговая</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr"/>
@@ -938,7 +938,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Если проверка уже на пороге</t>
+          <t>Если пришло требование или проверка</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Если сдавать нужно регулярно</t>
+          <t>Возьмём учёт и отчётность на себя</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Если вопрос оказался не разовым</t>
+          <t>Возьмём учёт и отчётность на себя</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Команда дешевле главбуха в штате</t>
+          <t>Возьмём учёт и отчётность на себя</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Нужен тот, кто будет вести учёт</t>
+          <t>Возьмём учёт и отчётность на себя</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>Исправим и возьмём учёт на себя</t>
+          <t>Возьмём учёт и отчётность на себя</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>Закроем то, что нашёл аудит</t>
+          <t>Приведём в порядок прошлые периоды</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr"/>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Схему нужно корректно вести</t>
+          <t>Возьмём учёт и отчётность на себя</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>Проведём через проверку ФНС</t>
+          <t>Если пришло требование или проверка</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr"/>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>Спор ведёт юрист, а не эксперт</t>
+          <t>Свой юрист без найма в штат</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>Бухгалтерия и юристы в одном месте</t>
+          <t>Возьмём учёт и отчётность на себя</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>Подтвердим сумму долга расчётом</t>
+          <t>Дадим заключение для суда</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>Учётные риски закроем тоже</t>
+          <t>Возьмём учёт и отчётность на себя</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>Проверим ещё и бухгалтерию</t>
+          <t>Проверим учёт раньше, чем налоговая</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr"/>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>Сменили директора — смените и бухгалтера</t>
+          <t>Возьмём учёт и отчётность на себя</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>Бухгалтерия с первого дня компании</t>
+          <t>Возьмём учёт и отчётность на себя</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>Учёт ВЭД своими силами ведут редко</t>
+          <t>Возьмём учёт и отчётность на себя</t>
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>Споры растут из ошибок в расчётах</t>
+          <t>Возьмём учёт и отчётность на себя</t>
         </is>
       </c>
       <c r="H78" s="11" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Если спор о цифрах и расчётах</t>
+          <t>Дадим заключение для суда</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>Сменить бухгалтера, пока не поздно</t>
+          <t>Возьмём учёт и отчётность на себя</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>Проверим учёт до прихода ФНС</t>
+          <t>Проверим учёт раньше, чем налоговая</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr"/>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>С бухгалтерией поможем тоже</t>
+          <t>Возьмём учёт и отчётность на себя</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>Когда вопрос сложнее вычета</t>
+          <t>Разберём вашу ситуацию предметно</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>Когда вопрос сложнее вычета</t>
+          <t>Разберём вашу ситуацию предметно</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>Когда вопрос сложнее вычета</t>
+          <t>Разберём вашу ситуацию предметно</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>Бухгалтерию возьмём на себя</t>
+          <t>Возьмём учёт и отчётность на себя</t>
         </is>
       </c>
       <c r="H110" s="11" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>Кадры и зарплату ведём тоже</t>
+          <t>Возьмём учёт и отчётность на себя</t>
         </is>
       </c>
       <c r="H114" s="11" t="inlineStr">

--- a/specs/perelinkovka-drugie-uslugi.xlsx
+++ b/specs/perelinkovka-drugie-uslugi.xlsx
@@ -2530,17 +2530,17 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Оптимизация налогообложения</t>
+          <t>Регистрация товарного знака</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>https://1-plus-1.ru/finansoviy-konsalting/optimizatsiya-nalogooblozheniya/</t>
+          <t>https://1-plus-1.ru/tovarnyye-znaki/</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>Законные способы платить меньше</t>
+          <t>Зарегистрируем бренд</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr"/>
@@ -2654,7 +2654,11 @@
           <t>Защитим вас в суде</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr"/>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>зелёная</t>
+        </is>
+      </c>
       <c r="I54" s="8" t="inlineStr"/>
     </row>
     <row r="55" ht="26" customHeight="1">
@@ -2756,24 +2760,20 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Судебная бухгалтерская экспертиза</t>
+          <t>Правовой аудит</t>
         </is>
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>https://1-plus-1.ru/finansoviy-konsalting/sudebnaya-bukhgalterskaya-i-finansovo-ekonomicheskaya-ekspertiza/</t>
+          <t>https://1-plus-1.ru/yuristy-dlya-biznesa/pravovoy-audit/</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>Дадим заключение для суда</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>зелёная</t>
-        </is>
-      </c>
+          <t>Найдём и устраним риски в документах</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr"/>
       <c r="I57" s="8" t="inlineStr"/>
     </row>
     <row r="58" ht="26" customHeight="1">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Тип 1</t>
+          <t>Тип 2</t>
         </is>
       </c>
       <c r="D62" s="10" t="n">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Бухгалтерское сопровождение</t>
+          <t>Регистрация и ликвидация бизнеса</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>https://1-plus-1.ru/bukhgalterskie-uslugi/abonentskoe-obsluzhivanie/</t>
+          <t>https://1-plus-1.ru/yuristy-dlya-biznesa/registratsiya-i-likvidatsiya/</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>Возьмём учёт и отчётность на себя</t>
-        </is>
-      </c>
-      <c r="H62" s="11" t="inlineStr">
-        <is>
-          <t>розовая</t>
+          <t>Регистрация ООО и ИП под ключ</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>зелёная</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr"/>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Тип 1</t>
+          <t>Тип 2</t>
         </is>
       </c>
       <c r="D63" s="10" t="n">
@@ -2990,20 +2990,24 @@
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Регистрация и ликвидация бизнеса</t>
+          <t>Юридическое обслуживание</t>
         </is>
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>https://1-plus-1.ru/yuristy-dlya-biznesa/registratsiya-i-likvidatsiya/</t>
+          <t>https://1-plus-1.ru/yuristy-dlya-biznesa/yuridicheskoe-obsluzhivanie/</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>Регистрация ООО и ИП под ключ</t>
-        </is>
-      </c>
-      <c r="H63" s="10" t="inlineStr"/>
+          <t>Свой юрист без найма в штат</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>зелёная</t>
+        </is>
+      </c>
       <c r="I63" s="8" t="inlineStr"/>
     </row>
     <row r="64" ht="26" customHeight="1">
@@ -3019,7 +3023,7 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Тип 1</t>
+          <t>Тип 2</t>
         </is>
       </c>
       <c r="D64" s="10" t="n">
@@ -3027,17 +3031,17 @@
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Юридическое обслуживание</t>
+          <t>Составление договоров</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>https://1-plus-1.ru/yuristy-dlya-biznesa/yuridicheskoe-obsluzhivanie/</t>
+          <t>https://1-plus-1.ru/yuristy-dlya-biznesa/sostavlenie-dogovorov/</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>Свой юрист без найма в штат</t>
+          <t>Договор, который защитит вас</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr"/>
@@ -3056,7 +3060,7 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Тип 1</t>
+          <t>Тип 2</t>
         </is>
       </c>
       <c r="D65" s="10" t="n">
@@ -3064,17 +3068,17 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Составление договоров</t>
+          <t>Юридическая консультация</t>
         </is>
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>https://1-plus-1.ru/yuristy-dlya-biznesa/sostavlenie-dogovorov/</t>
+          <t>https://1-plus-1.ru/yuristy-dlya-biznesa/yuridicheskie-uslugi/</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>Договор, который защитит вас</t>
+          <t>Ответим на правовой вопрос</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr"/>
@@ -3179,17 +3183,17 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Бухгалтерия для малого бизнеса</t>
+          <t>Заполнение деклараций</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>https://1-plus-1.ru/bukhgalterskie-uslugi/dlya-malogo-biznesa-/</t>
+          <t>https://1-plus-1.ru/bukhgalterskie-uslugi/zapolnenie-deklaratsiy/</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>Для небольших компаний и ИП</t>
+          <t>Подготовим и сдадим отчётность</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr"/>
@@ -3726,7 +3730,11 @@
           <t>От претензии до исполнительного листа</t>
         </is>
       </c>
-      <c r="H82" s="6" t="inlineStr"/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>зелёная</t>
+        </is>
+      </c>
       <c r="I82" s="4" t="inlineStr"/>
     </row>
     <row r="83" ht="26" customHeight="1">
@@ -3787,24 +3795,20 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Юридическое обслуживание</t>
+          <t>Регистрация товарного знака</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>https://1-plus-1.ru/yuristy-dlya-biznesa/yuridicheskoe-obsluzhivanie/</t>
+          <t>https://1-plus-1.ru/tovarnyye-znaki/</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>Свой юрист без найма в штат</t>
-        </is>
-      </c>
-      <c r="H84" s="7" t="inlineStr">
-        <is>
-          <t>зелёная</t>
-        </is>
-      </c>
+          <t>Зарегистрируем бренд</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr"/>
       <c r="I84" s="4" t="inlineStr"/>
     </row>
     <row r="85" ht="26" customHeight="1">
@@ -4103,17 +4107,17 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Оптимизация налогообложения</t>
+          <t>Юридическое обслуживание</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>https://1-plus-1.ru/finansoviy-konsalting/optimizatsiya-nalogooblozheniya/</t>
+          <t>https://1-plus-1.ru/yuristy-dlya-biznesa/yuridicheskoe-obsluzhivanie/</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>Законные способы платить меньше</t>
+          <t>Свой юрист без найма в штат</t>
         </is>
       </c>
       <c r="H92" s="6" t="inlineStr"/>
@@ -5064,17 +5068,17 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Споры в трудовых отношениях</t>
+          <t>Заполнение деклараций</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>https://1-plus-1.ru/yuristy-dlya-biznesa/spory-v-trudovykh-otnosheniyakh/</t>
+          <t>https://1-plus-1.ru/bukhgalterskie-uslugi/zapolnenie-deklaratsiy/</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>Защитим в споре с сотрудником</t>
+          <t>Подготовим и сдадим отчётность</t>
         </is>
       </c>
       <c r="H117" s="6" t="inlineStr"/>

--- a/specs/perelinkovka-drugie-uslugi.xlsx
+++ b/specs/perelinkovka-drugie-uslugi.xlsx
@@ -1232,17 +1232,17 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Юридическая консультация</t>
+          <t>Бухгалтерия для малого бизнеса</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>https://1-plus-1.ru/yuristy-dlya-biznesa/yuridicheskie-uslugi/</t>
+          <t>https://1-plus-1.ru/bukhgalterskie-uslugi/dlya-malogo-biznesa-/</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>Ответим на правовой вопрос</t>
+          <t>Для небольших компаний и ИП</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr"/>
